--- a/www/terminologies/CodeSystem-v2-0488.xlsx
+++ b/www/terminologies/CodeSystem-v2-0488.xlsx
@@ -115,7 +115,7 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0488|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0488</t>
   </si>
   <si>
     <t>Hierarchy</t>
